--- a/Analysis/Sensitivity_merec_entropy_arms_gemini.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_gemini.xlsx
@@ -481,7 +481,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -502,10 +502,10 @@
         <v>0.94256</v>
       </c>
       <c r="I2" t="n">
-        <v>0.03156000000000014</v>
+        <v>0.02283999999999997</v>
       </c>
       <c r="J2" t="n">
-        <v>0.93916</v>
+        <v>0.92888</v>
       </c>
     </row>
     <row r="3">
@@ -521,7 +521,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -530,22 +530,22 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6248799999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6812199999999999</v>
+        <v>0.67462</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7655399999999999</v>
+        <v>0.7605999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9412800000000001</v>
+        <v>0.93782</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03156000000000014</v>
+        <v>0.02283999999999997</v>
       </c>
       <c r="J3" t="n">
-        <v>0.93916</v>
+        <v>0.92888</v>
       </c>
     </row>
     <row r="4">
@@ -561,7 +561,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250328, "environmental": 0.246522, "comfort": 0.196918, "practicality": 0.306231}}</t>
+          <t>{"HVAC": {"energy_cost": 0.138244, "environmental": 0.127688, "comfort": 0.662899, "practicality": 0.071169}, "Appliance": {"energy_cost": 0.207971, "environmental": 0.043979, "comfort": 0.29187, "practicality": 0.45618}, "Shower": {"energy_cost": 0.250786, "environmental": 0.245387, "comfort": 0.20345, "practicality": 0.300377}}</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -570,22 +570,22 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.93916</v>
+        <v>0.92888</v>
       </c>
       <c r="F4" t="n">
-        <v>0.95434</v>
+        <v>0.9466800000000001</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9436</v>
+        <v>0.9385</v>
       </c>
       <c r="H4" t="n">
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>0.03156000000000014</v>
+        <v>0.02283999999999997</v>
       </c>
       <c r="J4" t="n">
-        <v>0.93916</v>
+        <v>0.92888</v>
       </c>
     </row>
     <row r="5">
@@ -601,7 +601,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -610,22 +610,22 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0.1706</v>
+        <v>0.16992</v>
       </c>
       <c r="F5" t="n">
-        <v>0.15588</v>
+        <v>0.15538</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3907600000000001</v>
+        <v>0.38974</v>
       </c>
       <c r="H5" t="n">
         <v>0.70052</v>
       </c>
       <c r="I5" t="n">
-        <v>0.16208</v>
+        <v>0.16968</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.9199999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -641,7 +641,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -650,22 +650,22 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0.33268</v>
+        <v>0.3396</v>
       </c>
       <c r="F6" t="n">
-        <v>0.3502999999999999</v>
+        <v>0.35702</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5204599999999999</v>
+        <v>0.5264800000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.81254</v>
+        <v>0.8145200000000001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.16208</v>
+        <v>0.16968</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.9199999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -681,7 +681,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.336687, "environmental": 0.316863, "comfort": 0.118531, "practicality": 0.22792}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336451, "environmental": 0.32038, "comfort": 0.269486, "practicality": 0.073683}, "Appliance": {"energy_cost": 0.193182, "environmental": 0.465156, "comfort": 0.123615, "practicality": 0.218047}, "Shower": {"energy_cost": 0.335356, "environmental": 0.315611, "comfort": 0.122014, "practicality": 0.227019}}</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -690,22 +690,22 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9271600000000001</v>
+        <v>0.9323</v>
       </c>
       <c r="G7" t="n">
-        <v>0.94564</v>
+        <v>0.95074</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9897</v>
+        <v>0.9949</v>
       </c>
       <c r="I7" t="n">
-        <v>0.16208</v>
+        <v>0.16968</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.9199999999999999</v>
       </c>
     </row>
     <row r="8">
@@ -742,7 +742,7 @@
         <v>0.83178</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1824399999999999</v>
+        <v>0.18462</v>
       </c>
       <c r="J8" t="n">
         <v>0.9315999999999999</v>
@@ -770,19 +770,19 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0.5902799999999999</v>
+        <v>0.59246</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6189199999999999</v>
+        <v>0.62336</v>
       </c>
       <c r="G9" t="n">
-        <v>0.68796</v>
+        <v>0.70056</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9131</v>
+        <v>0.914</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1824399999999999</v>
+        <v>0.18462</v>
       </c>
       <c r="J9" t="n">
         <v>0.9315999999999999</v>
@@ -822,7 +822,7 @@
         <v>0.9846</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1824399999999999</v>
+        <v>0.18462</v>
       </c>
       <c r="J10" t="n">
         <v>0.9315999999999999</v>
@@ -862,7 +862,7 @@
         <v>0.79694</v>
       </c>
       <c r="I11" t="n">
-        <v>0.02107999999999999</v>
+        <v>0.02532000000000001</v>
       </c>
       <c r="J11" t="n">
         <v>0.9350200000000001</v>
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>0.39542</v>
+        <v>0.39966</v>
       </c>
       <c r="F12" t="n">
-        <v>0.42454</v>
+        <v>0.43108</v>
       </c>
       <c r="G12" t="n">
-        <v>0.57058</v>
+        <v>0.58446</v>
       </c>
       <c r="H12" t="n">
-        <v>0.8313600000000001</v>
+        <v>0.8331200000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02107999999999999</v>
+        <v>0.02532000000000001</v>
       </c>
       <c r="J12" t="n">
         <v>0.9350200000000001</v>
@@ -942,7 +942,7 @@
         <v>0.9846</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02107999999999999</v>
+        <v>0.02532000000000001</v>
       </c>
       <c r="J13" t="n">
         <v>0.9350200000000001</v>
@@ -982,10 +982,10 @@
         <v>0.7097199999999999</v>
       </c>
       <c r="I14" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.08611999999999997</v>
       </c>
       <c r="J14" t="n">
-        <v>0.9193000000000001</v>
+        <v>0.90906</v>
       </c>
     </row>
     <row r="15">
@@ -1010,22 +1010,22 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.26844</v>
+        <v>0.26426</v>
       </c>
       <c r="F15" t="n">
-        <v>0.29162</v>
+        <v>0.29122</v>
       </c>
       <c r="G15" t="n">
-        <v>0.46388</v>
+        <v>0.46426</v>
       </c>
       <c r="H15" t="n">
-        <v>0.7894599999999999</v>
+        <v>0.78962</v>
       </c>
       <c r="I15" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.08611999999999997</v>
       </c>
       <c r="J15" t="n">
-        <v>0.9193000000000001</v>
+        <v>0.90906</v>
       </c>
     </row>
     <row r="16">
@@ -1050,22 +1050,22 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>0.9193000000000001</v>
+        <v>0.90906</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9395</v>
+        <v>0.9318</v>
       </c>
       <c r="G16" t="n">
-        <v>0.92616</v>
+        <v>0.91586</v>
       </c>
       <c r="H16" t="n">
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.09029999999999999</v>
+        <v>0.08611999999999997</v>
       </c>
       <c r="J16" t="n">
-        <v>0.9193000000000001</v>
+        <v>0.90906</v>
       </c>
     </row>
     <row r="17">
@@ -1090,22 +1090,22 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>0.16652</v>
+        <v>0.16992</v>
       </c>
       <c r="F17" t="n">
-        <v>0.15282</v>
+        <v>0.1554</v>
       </c>
       <c r="G17" t="n">
-        <v>0.38462</v>
+        <v>0.38976</v>
       </c>
       <c r="H17" t="n">
         <v>0.70052</v>
       </c>
       <c r="I17" t="n">
-        <v>0.16684</v>
+        <v>0.1662200000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.91654</v>
       </c>
     </row>
     <row r="18">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.33336</v>
+        <v>0.33614</v>
       </c>
       <c r="F18" t="n">
-        <v>0.35132</v>
+        <v>0.3544599999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5215</v>
+        <v>0.5213000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>0.81254</v>
+        <v>0.8145200000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.16684</v>
+        <v>0.1662200000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.91654</v>
       </c>
     </row>
     <row r="19">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.91654</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9271600000000001</v>
+        <v>0.9297599999999999</v>
       </c>
       <c r="G19" t="n">
         <v>0.94564</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9897</v>
+        <v>0.9949</v>
       </c>
       <c r="I19" t="n">
-        <v>0.16684</v>
+        <v>0.1662200000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9131400000000001</v>
+        <v>0.91654</v>
       </c>
     </row>
   </sheetData>

--- a/Analysis/Sensitivity_merec_entropy_arms_gemini.xlsx
+++ b/Analysis/Sensitivity_merec_entropy_arms_gemini.xlsx
@@ -961,7 +961,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>0.17814</v>
+        <v>0.17196</v>
       </c>
       <c r="F14" t="n">
-        <v>0.18052</v>
+        <v>0.1754</v>
       </c>
       <c r="G14" t="n">
-        <v>0.36822</v>
+        <v>0.35794</v>
       </c>
       <c r="H14" t="n">
-        <v>0.7097199999999999</v>
+        <v>0.7087</v>
       </c>
       <c r="I14" t="n">
-        <v>0.08611999999999997</v>
+        <v>0.08056000000000005</v>
       </c>
       <c r="J14" t="n">
         <v>0.90906</v>
@@ -1001,7 +1001,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1010,19 +1010,19 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>0.26426</v>
+        <v>0.25252</v>
       </c>
       <c r="F15" t="n">
-        <v>0.29122</v>
+        <v>0.27618</v>
       </c>
       <c r="G15" t="n">
-        <v>0.46426</v>
+        <v>0.44974</v>
       </c>
       <c r="H15" t="n">
-        <v>0.78962</v>
+        <v>0.7823800000000001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.08611999999999997</v>
+        <v>0.08056000000000005</v>
       </c>
       <c r="J15" t="n">
         <v>0.90906</v>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.248, "environmental": 0.244, "comfort": 0.203, "practicality": 0.305}}</t>
+          <t>{"HVAC": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Appliance": {"energy_cost": 0.3, "environmental": 0.35, "comfort": 0.2, "practicality": 0.15}, "Shower": {"energy_cost": 0.251251, "environmental": 0.245245, "comfort": 0.203203, "practicality": 0.3003}}</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1062,7 +1062,7 @@
         <v>1</v>
       </c>
       <c r="I16" t="n">
-        <v>0.08611999999999997</v>
+        <v>0.08056000000000005</v>
       </c>
       <c r="J16" t="n">
         <v>0.90906</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1093,19 +1093,19 @@
         <v>0.16992</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1554</v>
+        <v>0.15538</v>
       </c>
       <c r="G17" t="n">
-        <v>0.38976</v>
+        <v>0.38974</v>
       </c>
       <c r="H17" t="n">
         <v>0.70052</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1662200000000001</v>
+        <v>0.16968</v>
       </c>
       <c r="J17" t="n">
-        <v>0.91654</v>
+        <v>0.9199999999999999</v>
       </c>
     </row>
     <row r="18">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1130,22 +1130,22 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>0.33614</v>
+        <v>0.3396</v>
       </c>
       <c r="F18" t="n">
-        <v>0.3544599999999999</v>
+        <v>0.35702</v>
       </c>
       <c r="G18" t="n">
-        <v>0.5213000000000001</v>
+        <v>0.5264800000000001</v>
       </c>
       <c r="H18" t="n">
         <v>0.8145200000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1662200000000001</v>
+        <v>0.16968</v>
       </c>
       <c r="J18" t="n">
-        <v>0.91654</v>
+        <v>0.9199999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.333666, "environmental": 0.313686, "comfort": 0.126873, "practicality": 0.225774}}</t>
+          <t>{"HVAC": {"energy_cost": 0.336336, "environmental": 0.32032, "comfort": 0.269269, "practicality": 0.074074}, "Appliance": {"energy_cost": 0.193, "environmental": 0.465, "comfort": 0.124, "practicality": 0.218}, "Shower": {"energy_cost": 0.335, "environmental": 0.316, "comfort": 0.122, "practicality": 0.227}}</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1170,22 +1170,22 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>0.91654</v>
+        <v>0.9199999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9297599999999999</v>
+        <v>0.9323</v>
       </c>
       <c r="G19" t="n">
-        <v>0.94564</v>
+        <v>0.95074</v>
       </c>
       <c r="H19" t="n">
         <v>0.9949</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1662200000000001</v>
+        <v>0.16968</v>
       </c>
       <c r="J19" t="n">
-        <v>0.91654</v>
+        <v>0.9199999999999999</v>
       </c>
     </row>
   </sheetData>
